--- a/Example.xlsx
+++ b/Example.xlsx
@@ -92,11 +92,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
